--- a/Dune_Imperium_Card_Inventory.xlsx
+++ b/Dune_Imperium_Card_Inventory.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Imperium" sheetId="1" state="visible" r:id="rId2"/>
@@ -2470,7 +2470,7 @@
     <t xml:space="preserve">If you have a seat on the High Council and 2 DNA: +1 Victory Point</t>
   </si>
   <si>
-    <t xml:space="preserve">To the Victor …</t>
+    <t xml:space="preserve">To the Victor…</t>
   </si>
   <si>
     <t xml:space="preserve">When you win a Conflict: +3 Spice.
@@ -5809,7 +5809,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AK186"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15.65" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.65" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15"/>
@@ -18020,7 +18020,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
@@ -18714,7 +18714,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AB999"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="16.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="16.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.71"/>
@@ -49239,7 +49239,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P1000"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.3"/>
@@ -53396,7 +53396,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AG20"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
@@ -54720,7 +54720,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:V6"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
@@ -55148,7 +55148,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="14.29"/>
@@ -59500,7 +59500,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M37"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.86"/>
@@ -60601,7 +60601,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.29"/>
@@ -61240,7 +61240,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15"/>
@@ -61573,7 +61573,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="97.57"/>
   </cols>
@@ -61675,7 +61675,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="14.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="26.57"/>

--- a/Dune_Imperium_Card_Inventory.xlsx
+++ b/Dune_Imperium_Card_Inventory.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Imperium" sheetId="1" state="visible" r:id="rId2"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3057" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3056" uniqueCount="1141">
   <si>
     <t xml:space="preserve">Card Name</t>
   </si>
@@ -5808,8 +5808,8 @@
     <tabColor rgb="FFF6B26B"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AK186"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15.65" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AK1048576"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15.65" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15"/>
@@ -12037,9 +12037,7 @@
       <c r="O98" s="9"/>
       <c r="P98" s="9"/>
       <c r="Q98" s="9"/>
-      <c r="R98" s="9" t="s">
-        <v>40</v>
-      </c>
+      <c r="R98" s="9"/>
       <c r="S98" s="9"/>
       <c r="T98" s="9"/>
       <c r="U98" s="9"/>
@@ -17745,6 +17743,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="H1:H160"/>
   <conditionalFormatting sqref="A104:A186 A1:A101">
@@ -17887,7 +17886,7 @@
       <formula>NOT(ISERROR(SEARCH("Bloodlines",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E103">
+  <conditionalFormatting sqref="AB102">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17897,23 +17896,23 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB102">
+  <conditionalFormatting sqref="AC102">
     <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF4CCCC"/>
+        <color rgb="FFE67C73"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E103">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="max" val="0"/>
         <color rgb="FFCFE2F3"/>
         <color rgb="FF3D85C6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC102">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF4CCCC"/>
-        <color rgb="FFE67C73"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -18020,7 +18019,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
@@ -18714,7 +18713,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AB999"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="16.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="16.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.71"/>
@@ -49239,7 +49238,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P1000"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.3"/>
@@ -53396,7 +53395,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AG20"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
@@ -54720,7 +54719,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:V6"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
@@ -55148,7 +55147,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="14.29"/>
@@ -59500,7 +59499,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M37"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.86"/>
@@ -60601,7 +60600,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.29"/>
@@ -61240,7 +61239,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15"/>
@@ -61573,7 +61572,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="97.57"/>
   </cols>
@@ -61675,7 +61674,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="26.57"/>
